--- a/data/Updated_baggie_case_deployments.xlsx
+++ b/data/Updated_baggie_case_deployments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stlawu-my.sharepoint.com/personal/adfaut22_stlawu_edu/Documents/SLU Senior/Bio SYE/BirdNet_Analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F481FF25-D121-F54D-9770-F24C4D9CDE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{F481FF25-D121-F54D-9770-F24C4D9CDE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC32CC5A-B389-5241-8509-70591B4FCC46}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{7E8848E1-E179-F143-A1F6-74872CB44CF0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="249">
   <si>
     <t>AM0120</t>
   </si>
@@ -768,6 +768,21 @@
   </si>
   <si>
     <t>FLAG_comments</t>
+  </si>
+  <si>
+    <t>paired</t>
+  </si>
+  <si>
+    <t>paired_with</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>last_record</t>
   </si>
 </sst>
 </file>
@@ -863,7 +878,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -878,6 +893,9 @@
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -893,6 +911,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1212,10 +1234,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F28439-7079-E242-9602-8410DEF0126D}">
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AL31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="35" max="35" width="71" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>209</v>
       </c>
@@ -1321,8 +1346,17 @@
       <c r="AI1" s="13" t="s">
         <v>243</v>
       </c>
+      <c r="AJ1" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="AK1" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="AL1" s="14" t="s">
+        <v>248</v>
+      </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1412,8 +1446,17 @@
       <c r="AG2" s="1"/>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
+      <c r="AJ2" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL2" s="15">
+        <v>45849</v>
+      </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -1507,8 +1550,17 @@
       <c r="AG3" s="1"/>
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
+      <c r="AJ3" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL3" s="15">
+        <v>45830</v>
+      </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1600,8 +1652,14 @@
       <c r="AG4" s="1"/>
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
+      <c r="AJ4" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL4" s="15">
+        <v>45849</v>
+      </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
@@ -1693,8 +1751,17 @@
         <v>0</v>
       </c>
       <c r="AI5" s="1"/>
+      <c r="AJ5" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL5" s="15">
+        <v>45853</v>
+      </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
@@ -1784,8 +1851,17 @@
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
+      <c r="AJ6" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL6" s="15">
+        <v>45854</v>
+      </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -1883,8 +1959,14 @@
         <v>0</v>
       </c>
       <c r="AI7" s="1"/>
+      <c r="AJ7" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL7" s="15">
+        <v>45865</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>52</v>
       </c>
@@ -1982,8 +2064,14 @@
       <c r="AI8" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="AJ8" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL8" s="15">
+        <v>45867</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>60</v>
       </c>
@@ -2081,8 +2169,14 @@
         <v>0</v>
       </c>
       <c r="AI9" s="1"/>
+      <c r="AJ9" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL9" s="15">
+        <v>45878</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>68</v>
       </c>
@@ -2180,8 +2274,14 @@
         <v>0</v>
       </c>
       <c r="AI10" s="1"/>
+      <c r="AJ10" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL10" s="15">
+        <v>45883</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>76</v>
       </c>
@@ -2281,8 +2381,14 @@
         <v>0</v>
       </c>
       <c r="AI11" s="1"/>
+      <c r="AJ11" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL11" s="15">
+        <v>45886</v>
+      </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>83</v>
       </c>
@@ -2382,8 +2488,14 @@
         <v>0</v>
       </c>
       <c r="AI12" s="1"/>
+      <c r="AJ12" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL12" s="15">
+        <v>45886</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>91</v>
       </c>
@@ -2485,8 +2597,14 @@
       <c r="AI13" s="1" t="s">
         <v>98</v>
       </c>
+      <c r="AJ13" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL13" s="15">
+        <v>45888</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>99</v>
       </c>
@@ -2586,8 +2704,12 @@
       <c r="AI14" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="AJ14" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL14" s="16"/>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>107</v>
       </c>
@@ -2687,8 +2809,14 @@
       <c r="AI15" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="AJ15" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL15" s="15">
+        <v>45863</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>116</v>
       </c>
@@ -2788,8 +2916,14 @@
         <v>0</v>
       </c>
       <c r="AI16" s="1"/>
+      <c r="AJ16" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL16" s="15">
+        <v>45883</v>
+      </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>123</v>
       </c>
@@ -2889,8 +3023,14 @@
         <v>0</v>
       </c>
       <c r="AI17" s="1"/>
+      <c r="AJ17" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL17" s="15">
+        <v>45864</v>
+      </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>131</v>
       </c>
@@ -2984,8 +3124,14 @@
         <v>0</v>
       </c>
       <c r="AI18" s="1"/>
+      <c r="AJ18" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL18" s="15">
+        <v>45852</v>
+      </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>137</v>
       </c>
@@ -3081,8 +3227,17 @@
         <v>0</v>
       </c>
       <c r="AI19" s="1"/>
+      <c r="AJ19" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK19" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AL19" s="15">
+        <v>45853</v>
+      </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>144</v>
       </c>
@@ -3180,8 +3335,17 @@
         <v>0</v>
       </c>
       <c r="AI20" s="1"/>
+      <c r="AJ20" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="15">
+        <v>45852</v>
+      </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>149</v>
       </c>
@@ -3277,8 +3441,12 @@
       <c r="AI21" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="AJ21" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL21" s="16"/>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>154</v>
       </c>
@@ -3374,8 +3542,14 @@
         <v>0</v>
       </c>
       <c r="AI22" s="1"/>
+      <c r="AJ22" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL22" s="15">
+        <v>45887</v>
+      </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>160</v>
       </c>
@@ -3471,8 +3645,14 @@
         <v>0</v>
       </c>
       <c r="AI23" s="1"/>
+      <c r="AJ23" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL23" s="15">
+        <v>45866</v>
+      </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>168</v>
       </c>
@@ -3568,8 +3748,14 @@
         <v>0</v>
       </c>
       <c r="AI24" s="1"/>
+      <c r="AJ24" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL24" s="15">
+        <v>45889</v>
+      </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>175</v>
       </c>
@@ -3667,8 +3853,14 @@
         <v>0</v>
       </c>
       <c r="AI25" s="1"/>
+      <c r="AJ25" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL25" s="15">
+        <v>45853</v>
+      </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>181</v>
       </c>
@@ -3764,8 +3956,14 @@
         <v>0</v>
       </c>
       <c r="AI26" s="1"/>
+      <c r="AJ26" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL26" s="15">
+        <v>45854</v>
+      </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>188</v>
       </c>
@@ -3857,8 +4055,17 @@
         <v>0</v>
       </c>
       <c r="AI27" s="1"/>
+      <c r="AJ27" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK27" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL27" s="15">
+        <v>45853</v>
+      </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>191</v>
       </c>
@@ -3956,8 +4163,17 @@
         <v>0</v>
       </c>
       <c r="AI28" s="1"/>
+      <c r="AJ28" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK28" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AL28" s="15">
+        <v>45853</v>
+      </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>198</v>
       </c>
@@ -4053,8 +4269,17 @@
         <v>0</v>
       </c>
       <c r="AI29" s="1"/>
+      <c r="AJ29" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK29" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="AL29" s="15">
+        <v>45854</v>
+      </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>203</v>
       </c>
@@ -4150,8 +4375,14 @@
         <v>0</v>
       </c>
       <c r="AI30" s="1"/>
+      <c r="AJ30" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL30" s="15">
+        <v>45852</v>
+      </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -4247,6 +4478,15 @@
         <v>0</v>
       </c>
       <c r="AI31" s="1"/>
+      <c r="AJ31" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK31" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AL31" s="15">
+        <v>45852</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Updated_baggie_case_deployments.xlsx
+++ b/data/Updated_baggie_case_deployments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stlawu-my.sharepoint.com/personal/adfaut22_stlawu_edu/Documents/SLU Senior/Bio SYE/BirdNet_Analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{F481FF25-D121-F54D-9770-F24C4D9CDE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC32CC5A-B389-5241-8509-70591B4FCC46}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{F481FF25-D121-F54D-9770-F24C4D9CDE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D45DF764-7815-B542-AF70-1796E5293134}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{7E8848E1-E179-F143-A1F6-74872CB44CF0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="253">
   <si>
     <t>AM0120</t>
   </si>
@@ -783,6 +783,18 @@
   </si>
   <si>
     <t>last_record</t>
+  </si>
+  <si>
+    <t>paired_site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grasse River - Cranberry Lake Wild Forest </t>
+  </si>
+  <si>
+    <t>Oswegatchie Grassland Pond</t>
+  </si>
+  <si>
+    <t>Oswegatchie - Wolf/Moon lake</t>
   </si>
 </sst>
 </file>
@@ -1234,13 +1246,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F28439-7079-E242-9602-8410DEF0126D}">
-  <dimension ref="A1:AL31"/>
+  <dimension ref="A1:AM31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="35" max="35" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>209</v>
       </c>
@@ -1355,8 +1367,11 @@
       <c r="AL1" s="14" t="s">
         <v>248</v>
       </c>
+      <c r="AM1" s="14" t="s">
+        <v>249</v>
+      </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1455,8 +1470,11 @@
       <c r="AL2" s="15">
         <v>45849</v>
       </c>
+      <c r="AM2" t="s">
+        <v>250</v>
+      </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -1559,8 +1577,11 @@
       <c r="AL3" s="15">
         <v>45830</v>
       </c>
+      <c r="AM3" t="s">
+        <v>250</v>
+      </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1659,7 +1680,7 @@
         <v>45849</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
@@ -1760,8 +1781,11 @@
       <c r="AL5" s="15">
         <v>45853</v>
       </c>
+      <c r="AM5" t="s">
+        <v>251</v>
+      </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
@@ -1860,8 +1884,11 @@
       <c r="AL6" s="15">
         <v>45854</v>
       </c>
+      <c r="AM6" t="s">
+        <v>251</v>
+      </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -1966,7 +1993,7 @@
         <v>45865</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>52</v>
       </c>
@@ -2071,7 +2098,7 @@
         <v>45867</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>60</v>
       </c>
@@ -2176,7 +2203,7 @@
         <v>45878</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>68</v>
       </c>
@@ -2281,7 +2308,7 @@
         <v>45883</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>76</v>
       </c>
@@ -2388,7 +2415,7 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>83</v>
       </c>
@@ -2495,7 +2522,7 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>91</v>
       </c>
@@ -2604,7 +2631,7 @@
         <v>45888</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>99</v>
       </c>
@@ -2709,7 +2736,7 @@
       </c>
       <c r="AL14" s="16"/>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>107</v>
       </c>
@@ -2816,7 +2843,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>116</v>
       </c>
@@ -2923,7 +2950,7 @@
         <v>45883</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>123</v>
       </c>
@@ -3030,7 +3057,7 @@
         <v>45864</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>131</v>
       </c>
@@ -3131,7 +3158,7 @@
         <v>45852</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>137</v>
       </c>
@@ -3236,8 +3263,11 @@
       <c r="AL19" s="15">
         <v>45853</v>
       </c>
+      <c r="AM19" t="s">
+        <v>252</v>
+      </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>144</v>
       </c>
@@ -3344,8 +3374,11 @@
       <c r="AL20" s="15">
         <v>45852</v>
       </c>
+      <c r="AM20" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>149</v>
       </c>
@@ -3446,7 +3479,7 @@
       </c>
       <c r="AL21" s="16"/>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>154</v>
       </c>
@@ -3549,7 +3582,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>160</v>
       </c>
@@ -3652,7 +3685,7 @@
         <v>45866</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>168</v>
       </c>
@@ -3755,7 +3788,7 @@
         <v>45889</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>175</v>
       </c>
@@ -3860,7 +3893,7 @@
         <v>45853</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>181</v>
       </c>
@@ -3963,7 +3996,7 @@
         <v>45854</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>188</v>
       </c>
@@ -4064,8 +4097,11 @@
       <c r="AL27" s="15">
         <v>45853</v>
       </c>
+      <c r="AM27" t="s">
+        <v>252</v>
+      </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>191</v>
       </c>
@@ -4172,8 +4208,11 @@
       <c r="AL28" s="15">
         <v>45853</v>
       </c>
+      <c r="AM28" t="s">
+        <v>193</v>
+      </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>198</v>
       </c>
@@ -4278,8 +4317,11 @@
       <c r="AL29" s="15">
         <v>45854</v>
       </c>
+      <c r="AM29" t="s">
+        <v>193</v>
+      </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>203</v>
       </c>
@@ -4382,7 +4424,7 @@
         <v>45852</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -4487,6 +4529,9 @@
       <c r="AL31" s="15">
         <v>45852</v>
       </c>
+      <c r="AM31" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
